--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132335807</v>
+        <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96501</v>
+        <v>96660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,37 +2148,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348516</v>
+        <v>348521</v>
       </c>
       <c r="R15" t="n">
-        <v>6519293</v>
+        <v>6519371</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,33 +2218,28 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>På ek.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335807</t>
+          <t>https://artportalen.se/Sighting/136707418</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132335809</v>
+        <v>132335807</v>
       </c>
       <c r="B16" t="n">
         <v>96501</v>
@@ -2275,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348379</v>
+        <v>348516</v>
       </c>
       <c r="R16" t="n">
-        <v>6519389</v>
+        <v>6519293</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2323,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>På ek.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2345,13 +2340,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335809</t>
+          <t>https://artportalen.se/Sighting/132335807</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132446043</v>
+        <v>132335809</v>
       </c>
       <c r="B17" t="n">
         <v>96501</v>
@@ -2382,17 +2377,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348552</v>
+        <v>348379</v>
       </c>
       <c r="R17" t="n">
-        <v>6519205</v>
+        <v>6519389</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,12 +2411,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,28 +2427,33 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>På ek och berg.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446043</t>
+          <t>https://artportalen.se/Sighting/132335809</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132446047</v>
+        <v>132446043</v>
       </c>
       <c r="B18" t="n">
         <v>96501</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348480</v>
+        <v>348552</v>
       </c>
       <c r="R18" t="n">
-        <v>6519264</v>
+        <v>6519205</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2549,13 +2549,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446047</t>
+          <t>https://artportalen.se/Sighting/132446043</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132446048</v>
+        <v>132446047</v>
       </c>
       <c r="B19" t="n">
         <v>96501</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R19" t="n">
-        <v>6519312</v>
+        <v>6519264</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2651,13 +2651,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446048</t>
+          <t>https://artportalen.se/Sighting/132446047</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446054</v>
+        <v>132446048</v>
       </c>
       <c r="B20" t="n">
         <v>96501</v>
@@ -2688,14 +2688,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348384</v>
+        <v>348482</v>
       </c>
       <c r="R20" t="n">
-        <v>6519382</v>
+        <v>6519312</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,13 +2753,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446054</t>
+          <t>https://artportalen.se/Sighting/132446048</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446055</v>
+        <v>132446054</v>
       </c>
       <c r="B21" t="n">
         <v>96501</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348415</v>
+        <v>348384</v>
       </c>
       <c r="R21" t="n">
-        <v>6519441</v>
+        <v>6519382</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2855,13 +2855,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446055</t>
+          <t>https://artportalen.se/Sighting/132446054</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132446062</v>
+        <v>132446055</v>
       </c>
       <c r="B22" t="n">
         <v>96501</v>
@@ -2892,14 +2892,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348457</v>
+        <v>348415</v>
       </c>
       <c r="R22" t="n">
-        <v>6519522</v>
+        <v>6519441</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,16 +2957,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446062</t>
+          <t>https://artportalen.se/Sighting/132446055</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136097925</v>
+        <v>132446062</v>
       </c>
       <c r="B23" t="n">
-        <v>96648</v>
+        <v>96501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,14 +2994,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348567</v>
+        <v>348457</v>
       </c>
       <c r="R23" t="n">
-        <v>6519639</v>
+        <v>6519522</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,16 +3059,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097925</t>
+          <t>https://artportalen.se/Sighting/132446062</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132397692</v>
+        <v>136097925</v>
       </c>
       <c r="B24" t="n">
-        <v>96261</v>
+        <v>96649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,37 +3076,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348539</v>
+        <v>348567</v>
       </c>
       <c r="R24" t="n">
-        <v>6519214</v>
+        <v>6519639</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,33 +3146,28 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132397692</t>
+          <t>https://artportalen.se/Sighting/136097925</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446060</v>
+        <v>132397692</v>
       </c>
       <c r="B25" t="n">
         <v>96261</v>
@@ -3203,17 +3198,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348457</v>
+        <v>348539</v>
       </c>
       <c r="R25" t="n">
-        <v>6519520</v>
+        <v>6519214</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3237,12 +3232,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,31 +3248,36 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446060</t>
+          <t>https://artportalen.se/Sighting/132397692</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132335999</v>
+        <v>132446060</v>
       </c>
       <c r="B26" t="n">
-        <v>96306</v>
+        <v>96261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3285,37 +3285,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348539</v>
+        <v>348457</v>
       </c>
       <c r="R26" t="n">
-        <v>6519214</v>
+        <v>6519520</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,33 +3355,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335999</t>
+          <t>https://artportalen.se/Sighting/132446060</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132446045</v>
+        <v>132335999</v>
       </c>
       <c r="B27" t="n">
         <v>96306</v>
@@ -3412,17 +3407,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348545</v>
+        <v>348539</v>
       </c>
       <c r="R27" t="n">
-        <v>6519237</v>
+        <v>6519214</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3446,12 +3441,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,28 +3457,33 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446045</t>
+          <t>https://artportalen.se/Sighting/132335999</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446059</v>
+        <v>132446045</v>
       </c>
       <c r="B28" t="n">
         <v>96306</v>
@@ -3514,14 +3514,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348464</v>
+        <v>348545</v>
       </c>
       <c r="R28" t="n">
-        <v>6519521</v>
+        <v>6519237</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3579,16 +3579,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446059</t>
+          <t>https://artportalen.se/Sighting/132446045</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132335439</v>
+        <v>132446059</v>
       </c>
       <c r="B29" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,37 +3596,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348505</v>
+        <v>348464</v>
       </c>
       <c r="R29" t="n">
-        <v>6519139</v>
+        <v>6519521</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,41 +3666,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335439</t>
+          <t>https://artportalen.se/Sighting/132446059</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136097899</v>
+        <v>132335439</v>
       </c>
       <c r="B30" t="n">
-        <v>96680</v>
+        <v>96533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3728,17 +3718,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348719</v>
+        <v>348505</v>
       </c>
       <c r="R30" t="n">
-        <v>6519093</v>
+        <v>6519139</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3762,12 +3752,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,45 +3769,40 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097899</t>
+          <t>https://artportalen.se/Sighting/132335439</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136097906</v>
+        <v>136097899</v>
       </c>
       <c r="B31" t="n">
-        <v>96680</v>
+        <v>96681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3849,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348560</v>
+        <v>348719</v>
       </c>
       <c r="R31" t="n">
-        <v>6519339</v>
+        <v>6519093</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3925,16 +3910,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097906</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136097907</v>
+        <v>136097906</v>
       </c>
       <c r="B32" t="n">
-        <v>96680</v>
+        <v>96681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,10 +3951,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348545</v>
+        <v>348560</v>
       </c>
       <c r="R32" t="n">
-        <v>6519374</v>
+        <v>6519339</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4042,16 +4027,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097907</t>
+          <t>https://artportalen.se/Sighting/136097906</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132335525</v>
+        <v>136097907</v>
       </c>
       <c r="B33" t="n">
-        <v>57972</v>
+        <v>96681</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,49 +4044,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348462</v>
+        <v>348545</v>
       </c>
       <c r="R33" t="n">
-        <v>6519162</v>
+        <v>6519374</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4125,12 +4098,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,71 +4114,81 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335525</t>
+          <t>https://artportalen.se/Sighting/136097907</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446065</v>
+        <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>4776</v>
+        <v>91590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100299</v>
+        <v>5741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348443</v>
+        <v>348504</v>
       </c>
       <c r="R34" t="n">
-        <v>6519628</v>
+        <v>6519183</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4232,37 +4215,23 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4278,16 +4247,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446065</t>
+          <t>https://artportalen.se/Sighting/136707421</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446063</v>
+        <v>132335525</v>
       </c>
       <c r="B35" t="n">
-        <v>5201</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4295,16 +4264,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4312,25 +4281,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348439</v>
+        <v>348462</v>
       </c>
       <c r="R35" t="n">
-        <v>6519636</v>
+        <v>6519162</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4354,12 +4330,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4370,46 +4346,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446063</t>
+          <t>https://artportalen.se/Sighting/132335525</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446064</v>
+        <v>132446065</v>
       </c>
       <c r="B36" t="n">
-        <v>5201</v>
+        <v>4776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,21 +4378,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4522,13 +4483,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446064</t>
+          <t>https://artportalen.se/Sighting/132446065</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446066</v>
+        <v>132446063</v>
       </c>
       <c r="B37" t="n">
         <v>5201</v>
@@ -4559,7 +4520,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4568,10 +4529,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348507</v>
+        <v>348439</v>
       </c>
       <c r="R37" t="n">
-        <v>6519811</v>
+        <v>6519636</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4644,38 +4605,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446066</t>
+          <t>https://artportalen.se/Sighting/132446063</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132446029</v>
+        <v>132446064</v>
       </c>
       <c r="B38" t="n">
-        <v>8374</v>
+        <v>5201</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106540</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4686,14 +4647,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348623</v>
+        <v>348443</v>
       </c>
       <c r="R38" t="n">
-        <v>6519241</v>
+        <v>6519628</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4739,17 +4700,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4766,16 +4727,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132446064</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132446056</v>
+        <v>132446066</v>
       </c>
       <c r="B39" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,27 +4744,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4812,10 +4773,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348430</v>
+        <v>348507</v>
       </c>
       <c r="R39" t="n">
-        <v>6519483</v>
+        <v>6519811</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4861,17 +4822,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4888,16 +4849,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446056</t>
+          <t>https://artportalen.se/Sighting/132446066</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132446053</v>
+        <v>132446029</v>
       </c>
       <c r="B40" t="n">
-        <v>111471</v>
+        <v>8374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4905,34 +4866,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348463</v>
+        <v>348623</v>
       </c>
       <c r="R40" t="n">
-        <v>6519366</v>
+        <v>6519241</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4976,6 +4942,21 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
@@ -4990,51 +4971,56 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446053</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136097900</v>
+        <v>132446056</v>
       </c>
       <c r="B41" t="n">
-        <v>111643</v>
+        <v>8460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348618</v>
+        <v>348430</v>
       </c>
       <c r="R41" t="n">
-        <v>6519260</v>
+        <v>6519483</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5061,12 +5047,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5077,6 +5063,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5092,64 +5093,54 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/132446056</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121791871</v>
+        <v>132446053</v>
       </c>
       <c r="B42" t="n">
-        <v>101326</v>
+        <v>111471</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348561</v>
+        <v>348463</v>
       </c>
       <c r="R42" t="n">
-        <v>6519216</v>
+        <v>6519366</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5173,12 +5164,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5189,84 +5180,69 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791871</t>
+          <t>https://artportalen.se/Sighting/132446053</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121792063</v>
+        <v>136097900</v>
       </c>
       <c r="B43" t="n">
-        <v>101326</v>
+        <v>111644</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348553</v>
+        <v>348618</v>
       </c>
       <c r="R43" t="n">
-        <v>6519199</v>
+        <v>6519260</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5290,12 +5266,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,36 +5282,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792063</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121792253</v>
+        <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>101326</v>
+        <v>106399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,47 +5314,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348514</v>
+        <v>348660</v>
       </c>
       <c r="R44" t="n">
-        <v>6519160</v>
+        <v>6519138</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5407,12 +5368,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5423,33 +5384,28 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792253</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121792318</v>
+        <v>121791871</v>
       </c>
       <c r="B45" t="n">
         <v>101326</v>
@@ -5494,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348459</v>
+        <v>348561</v>
       </c>
       <c r="R45" t="n">
-        <v>6519139</v>
+        <v>6519216</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5543,7 +5499,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5560,13 +5516,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792318</t>
+          <t>https://artportalen.se/Sighting/121791871</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121792399</v>
+        <v>121792063</v>
       </c>
       <c r="B46" t="n">
         <v>101326</v>
@@ -5611,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348481</v>
+        <v>348553</v>
       </c>
       <c r="R46" t="n">
-        <v>6519252</v>
+        <v>6519199</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,13 +5633,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792399</t>
+          <t>https://artportalen.se/Sighting/121792063</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121792568</v>
+        <v>121792253</v>
       </c>
       <c r="B47" t="n">
         <v>101326</v>
@@ -5724,14 +5680,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348486</v>
+        <v>348514</v>
       </c>
       <c r="R47" t="n">
-        <v>6519336</v>
+        <v>6519160</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5794,13 +5750,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792568</t>
+          <t>https://artportalen.se/Sighting/121792253</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121792607</v>
+        <v>121792318</v>
       </c>
       <c r="B48" t="n">
         <v>101326</v>
@@ -5841,14 +5797,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348455</v>
+        <v>348459</v>
       </c>
       <c r="R48" t="n">
-        <v>6519346</v>
+        <v>6519139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5911,16 +5867,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792607</t>
+          <t>https://artportalen.se/Sighting/121792318</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132335808</v>
+        <v>121792399</v>
       </c>
       <c r="B49" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5946,16 +5902,26 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
         <v>348481</v>
       </c>
       <c r="R49" t="n">
-        <v>6519286</v>
+        <v>6519252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5982,12 +5948,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5998,31 +5964,36 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335808</t>
+          <t>https://artportalen.se/Sighting/121792399</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132336006</v>
+        <v>121792568</v>
       </c>
       <c r="B50" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6048,16 +6019,26 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>348550</v>
+        <v>348486</v>
       </c>
       <c r="R50" t="n">
-        <v>6519223</v>
+        <v>6519336</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6084,12 +6065,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6101,35 +6082,35 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336006</t>
+          <t>https://artportalen.se/Sighting/121792568</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132336196</v>
+        <v>121792607</v>
       </c>
       <c r="B51" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6155,16 +6136,26 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348529</v>
+        <v>348455</v>
       </c>
       <c r="R51" t="n">
-        <v>6519171</v>
+        <v>6519346</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6191,12 +6182,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6208,32 +6199,32 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336196</t>
+          <t>https://artportalen.se/Sighting/121792607</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132336478</v>
+        <v>132335808</v>
       </c>
       <c r="B52" t="n">
         <v>101403</v>
@@ -6264,14 +6255,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>348493</v>
+        <v>348481</v>
       </c>
       <c r="R52" t="n">
-        <v>6519126</v>
+        <v>6519286</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6329,13 +6320,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336478</t>
+          <t>https://artportalen.se/Sighting/132335808</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132446046</v>
+        <v>132336006</v>
       </c>
       <c r="B53" t="n">
         <v>101403</v>
@@ -6366,17 +6357,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>348506</v>
+        <v>348550</v>
       </c>
       <c r="R53" t="n">
-        <v>6519266</v>
+        <v>6519223</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6400,12 +6391,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6416,28 +6407,33 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446046</t>
+          <t>https://artportalen.se/Sighting/132336006</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132446050</v>
+        <v>132336196</v>
       </c>
       <c r="B54" t="n">
         <v>101403</v>
@@ -6468,17 +6464,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>348486</v>
+        <v>348529</v>
       </c>
       <c r="R54" t="n">
-        <v>6519319</v>
+        <v>6519171</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6502,12 +6498,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6518,28 +6514,33 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446050</t>
+          <t>https://artportalen.se/Sighting/132336196</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132446052</v>
+        <v>132336478</v>
       </c>
       <c r="B55" t="n">
         <v>101403</v>
@@ -6570,17 +6571,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>348480</v>
+        <v>348493</v>
       </c>
       <c r="R55" t="n">
-        <v>6519355</v>
+        <v>6519126</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6604,12 +6605,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6624,27 +6625,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446052</t>
+          <t>https://artportalen.se/Sighting/132336478</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132336005</v>
+        <v>132446046</v>
       </c>
       <c r="B56" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6652,37 +6653,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>348550</v>
+        <v>348506</v>
       </c>
       <c r="R56" t="n">
-        <v>6519223</v>
+        <v>6519266</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6706,12 +6707,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6722,36 +6723,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336005</t>
+          <t>https://artportalen.se/Sighting/132446046</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132446061</v>
+        <v>132446050</v>
       </c>
       <c r="B57" t="n">
-        <v>80403</v>
+        <v>101403</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6759,34 +6755,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003719</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>348457</v>
+        <v>348486</v>
       </c>
       <c r="R57" t="n">
-        <v>6519520</v>
+        <v>6519319</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6843,6 +6839,317 @@
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132336005</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336005</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132446061</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>348457</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6519520</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446061</t>
         </is>
@@ -6906,6 +7213,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96660</v>
+        <v>96665</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>106399</v>
+        <v>106404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96665</v>
+        <v>96667</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>106404</v>
+        <v>106406</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96667</v>
+        <v>96673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96673</v>
+        <v>96675</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -4370,7 +4370,7 @@
         <v>132446065</v>
       </c>
       <c r="B36" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96675</v>
+        <v>96676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2140,7 +2140,7 @@
         <v>136707418</v>
       </c>
       <c r="B15" t="n">
-        <v>96676</v>
+        <v>96682</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>136707421</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>136707423</v>
       </c>
       <c r="B44" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,45 +1378,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132446051</v>
+        <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>92647</v>
+        <v>89301</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>805</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>348495</v>
+        <v>348566</v>
       </c>
       <c r="R8" t="n">
-        <v>6519363</v>
+        <v>6519182</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,21 +1459,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,16 +1474,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446051</t>
+          <t>https://artportalen.se/Sighting/137153571</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132335997</v>
+        <v>132446051</v>
       </c>
       <c r="B9" t="n">
-        <v>96019</v>
+        <v>92647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,37 +1491,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2362</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>348539</v>
+        <v>348495</v>
       </c>
       <c r="R9" t="n">
-        <v>6519214</v>
+        <v>6519363</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,12 +1545,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,35 +1562,45 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335997</t>
+          <t>https://artportalen.se/Sighting/132446051</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132397690</v>
+        <v>132335997</v>
       </c>
       <c r="B10" t="n">
-        <v>97888</v>
+        <v>96019</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,21 +1608,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2604</v>
+        <v>2362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1703,16 +1698,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132397690</t>
+          <t>https://artportalen.se/Sighting/132335997</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132336000</v>
+        <v>132397690</v>
       </c>
       <c r="B11" t="n">
-        <v>96512</v>
+        <v>97888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1810,13 +1805,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336000</t>
+          <t>https://artportalen.se/Sighting/132397690</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132446044</v>
+        <v>132336000</v>
       </c>
       <c r="B12" t="n">
         <v>96512</v>
@@ -1847,17 +1842,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348545</v>
+        <v>348539</v>
       </c>
       <c r="R12" t="n">
-        <v>6519237</v>
+        <v>6519214</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,12 +1876,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,28 +1892,33 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446044</t>
+          <t>https://artportalen.se/Sighting/132336000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132446058</v>
+        <v>132446044</v>
       </c>
       <c r="B13" t="n">
         <v>96512</v>
@@ -1949,14 +1949,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348464</v>
+        <v>348545</v>
       </c>
       <c r="R13" t="n">
-        <v>6519509</v>
+        <v>6519237</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2014,16 +2014,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446058</t>
+          <t>https://artportalen.se/Sighting/132446044</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136097908</v>
+        <v>132446058</v>
       </c>
       <c r="B14" t="n">
-        <v>96660</v>
+        <v>96512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,14 +2051,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348516</v>
+        <v>348464</v>
       </c>
       <c r="R14" t="n">
-        <v>6519369</v>
+        <v>6519509</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,21 +2101,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2131,16 +2116,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097908</t>
+          <t>https://artportalen.se/Sighting/132446058</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136707418</v>
+        <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96682</v>
+        <v>96660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,14 +2153,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348521</v>
+        <v>348516</v>
       </c>
       <c r="R15" t="n">
-        <v>6519371</v>
+        <v>6519369</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2202,12 +2187,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,6 +2203,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2233,16 +2233,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707418</t>
+          <t>https://artportalen.se/Sighting/136097908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132335807</v>
+        <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96501</v>
+        <v>96686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,37 +2250,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348516</v>
+        <v>348521</v>
       </c>
       <c r="R16" t="n">
-        <v>6519293</v>
+        <v>6519371</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,33 +2320,28 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>På ek.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335807</t>
+          <t>https://artportalen.se/Sighting/136707418</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132335809</v>
+        <v>132335807</v>
       </c>
       <c r="B17" t="n">
         <v>96501</v>
@@ -2377,14 +2372,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348379</v>
+        <v>348516</v>
       </c>
       <c r="R17" t="n">
-        <v>6519389</v>
+        <v>6519293</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,7 +2425,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>På ek.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2447,13 +2442,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335809</t>
+          <t>https://artportalen.se/Sighting/132335807</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132446043</v>
+        <v>132335809</v>
       </c>
       <c r="B18" t="n">
         <v>96501</v>
@@ -2484,17 +2479,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348552</v>
+        <v>348379</v>
       </c>
       <c r="R18" t="n">
-        <v>6519205</v>
+        <v>6519389</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2518,12 +2513,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,28 +2529,33 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>På ek och berg.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446043</t>
+          <t>https://artportalen.se/Sighting/132335809</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132446047</v>
+        <v>132446043</v>
       </c>
       <c r="B19" t="n">
         <v>96501</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348480</v>
+        <v>348552</v>
       </c>
       <c r="R19" t="n">
-        <v>6519264</v>
+        <v>6519205</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2651,13 +2651,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446047</t>
+          <t>https://artportalen.se/Sighting/132446043</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446048</v>
+        <v>132446047</v>
       </c>
       <c r="B20" t="n">
         <v>96501</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R20" t="n">
-        <v>6519312</v>
+        <v>6519264</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,13 +2753,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446048</t>
+          <t>https://artportalen.se/Sighting/132446047</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446054</v>
+        <v>132446048</v>
       </c>
       <c r="B21" t="n">
         <v>96501</v>
@@ -2790,14 +2790,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348384</v>
+        <v>348482</v>
       </c>
       <c r="R21" t="n">
-        <v>6519382</v>
+        <v>6519312</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2855,13 +2855,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446054</t>
+          <t>https://artportalen.se/Sighting/132446048</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132446055</v>
+        <v>132446054</v>
       </c>
       <c r="B22" t="n">
         <v>96501</v>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348415</v>
+        <v>348384</v>
       </c>
       <c r="R22" t="n">
-        <v>6519441</v>
+        <v>6519382</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446055</t>
+          <t>https://artportalen.se/Sighting/132446054</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132446062</v>
+        <v>132446055</v>
       </c>
       <c r="B23" t="n">
         <v>96501</v>
@@ -2994,14 +2994,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348457</v>
+        <v>348415</v>
       </c>
       <c r="R23" t="n">
-        <v>6519522</v>
+        <v>6519441</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3059,16 +3059,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446062</t>
+          <t>https://artportalen.se/Sighting/132446055</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136097925</v>
+        <v>132446062</v>
       </c>
       <c r="B24" t="n">
-        <v>96649</v>
+        <v>96501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3096,14 +3096,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348567</v>
+        <v>348457</v>
       </c>
       <c r="R24" t="n">
-        <v>6519639</v>
+        <v>6519522</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,16 +3161,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097925</t>
+          <t>https://artportalen.se/Sighting/132446062</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132397692</v>
+        <v>136097925</v>
       </c>
       <c r="B25" t="n">
-        <v>96261</v>
+        <v>96649</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,37 +3178,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348539</v>
+        <v>348567</v>
       </c>
       <c r="R25" t="n">
-        <v>6519214</v>
+        <v>6519639</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,33 +3248,28 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132397692</t>
+          <t>https://artportalen.se/Sighting/136097925</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446060</v>
+        <v>132397692</v>
       </c>
       <c r="B26" t="n">
         <v>96261</v>
@@ -3305,17 +3300,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348457</v>
+        <v>348539</v>
       </c>
       <c r="R26" t="n">
-        <v>6519520</v>
+        <v>6519214</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3339,12 +3334,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,31 +3350,36 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446060</t>
+          <t>https://artportalen.se/Sighting/132397692</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132335999</v>
+        <v>132446060</v>
       </c>
       <c r="B27" t="n">
-        <v>96306</v>
+        <v>96261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,37 +3387,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348539</v>
+        <v>348457</v>
       </c>
       <c r="R27" t="n">
-        <v>6519214</v>
+        <v>6519520</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3441,12 +3441,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,33 +3457,28 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335999</t>
+          <t>https://artportalen.se/Sighting/132446060</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446045</v>
+        <v>132335999</v>
       </c>
       <c r="B28" t="n">
         <v>96306</v>
@@ -3514,17 +3509,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348545</v>
+        <v>348539</v>
       </c>
       <c r="R28" t="n">
-        <v>6519237</v>
+        <v>6519214</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3548,12 +3543,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,28 +3559,33 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446045</t>
+          <t>https://artportalen.se/Sighting/132335999</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446059</v>
+        <v>132446045</v>
       </c>
       <c r="B29" t="n">
         <v>96306</v>
@@ -3616,14 +3616,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348464</v>
+        <v>348545</v>
       </c>
       <c r="R29" t="n">
-        <v>6519521</v>
+        <v>6519237</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3681,16 +3681,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446059</t>
+          <t>https://artportalen.se/Sighting/132446045</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132335439</v>
+        <v>132446059</v>
       </c>
       <c r="B30" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,37 +3698,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348505</v>
+        <v>348464</v>
       </c>
       <c r="R30" t="n">
-        <v>6519139</v>
+        <v>6519521</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,41 +3768,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335439</t>
+          <t>https://artportalen.se/Sighting/132446059</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136097899</v>
+        <v>132335439</v>
       </c>
       <c r="B31" t="n">
-        <v>96681</v>
+        <v>96533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3830,17 +3820,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348719</v>
+        <v>348505</v>
       </c>
       <c r="R31" t="n">
-        <v>6519093</v>
+        <v>6519139</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3864,12 +3854,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,42 +3871,37 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097899</t>
+          <t>https://artportalen.se/Sighting/132335439</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136097906</v>
+        <v>136097899</v>
       </c>
       <c r="B32" t="n">
         <v>96681</v>
@@ -3951,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348560</v>
+        <v>348719</v>
       </c>
       <c r="R32" t="n">
-        <v>6519339</v>
+        <v>6519093</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4027,13 +4012,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097906</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136097907</v>
+        <v>136097906</v>
       </c>
       <c r="B33" t="n">
         <v>96681</v>
@@ -4068,10 +4053,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348545</v>
+        <v>348560</v>
       </c>
       <c r="R33" t="n">
-        <v>6519374</v>
+        <v>6519339</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4144,51 +4129,51 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097907</t>
+          <t>https://artportalen.se/Sighting/136097906</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136707421</v>
+        <v>136097907</v>
       </c>
       <c r="B34" t="n">
-        <v>91605</v>
+        <v>96681</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5741</v>
+        <v>2818</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348504</v>
+        <v>348545</v>
       </c>
       <c r="R34" t="n">
-        <v>6519183</v>
+        <v>6519374</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4215,23 +4200,37 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4247,16 +4246,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707421</t>
+          <t>https://artportalen.se/Sighting/136097907</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132335525</v>
+        <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>57972</v>
+        <v>93098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4264,49 +4263,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348462</v>
+        <v>348552</v>
       </c>
       <c r="R35" t="n">
-        <v>6519162</v>
+        <v>6519663</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4330,12 +4317,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,67 +4337,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335525</t>
+          <t>https://artportalen.se/Sighting/137153576</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446065</v>
+        <v>136707421</v>
       </c>
       <c r="B36" t="n">
-        <v>4777</v>
+        <v>91609</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100299</v>
+        <v>5741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348443</v>
+        <v>348504</v>
       </c>
       <c r="R36" t="n">
-        <v>6519628</v>
+        <v>6519183</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4437,37 +4419,23 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4483,16 +4451,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446065</t>
+          <t>https://artportalen.se/Sighting/136707421</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446063</v>
+        <v>132335525</v>
       </c>
       <c r="B37" t="n">
-        <v>5201</v>
+        <v>57972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,16 +4468,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4517,25 +4485,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348439</v>
+        <v>348462</v>
       </c>
       <c r="R37" t="n">
-        <v>6519636</v>
+        <v>6519162</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4559,12 +4534,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4575,46 +4550,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446063</t>
+          <t>https://artportalen.se/Sighting/132335525</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132446064</v>
+        <v>132446065</v>
       </c>
       <c r="B38" t="n">
-        <v>5201</v>
+        <v>4777</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,21 +4582,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,13 +4687,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446064</t>
+          <t>https://artportalen.se/Sighting/132446065</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132446066</v>
+        <v>132446063</v>
       </c>
       <c r="B39" t="n">
         <v>5201</v>
@@ -4764,7 +4724,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4773,10 +4733,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348507</v>
+        <v>348439</v>
       </c>
       <c r="R39" t="n">
-        <v>6519811</v>
+        <v>6519636</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4849,38 +4809,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446066</t>
+          <t>https://artportalen.se/Sighting/132446063</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132446029</v>
+        <v>132446064</v>
       </c>
       <c r="B40" t="n">
-        <v>8374</v>
+        <v>5201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106540</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4891,14 +4851,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348623</v>
+        <v>348443</v>
       </c>
       <c r="R40" t="n">
-        <v>6519241</v>
+        <v>6519628</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4944,17 +4904,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4971,16 +4931,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132446064</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446056</v>
+        <v>132446066</v>
       </c>
       <c r="B41" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4988,27 +4948,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5017,10 +4977,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348430</v>
+        <v>348507</v>
       </c>
       <c r="R41" t="n">
-        <v>6519483</v>
+        <v>6519811</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5066,17 +5026,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5093,16 +5053,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446056</t>
+          <t>https://artportalen.se/Sighting/132446066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132446053</v>
+        <v>132446029</v>
       </c>
       <c r="B42" t="n">
-        <v>111471</v>
+        <v>8374</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,34 +5070,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348463</v>
+        <v>348623</v>
       </c>
       <c r="R42" t="n">
-        <v>6519366</v>
+        <v>6519241</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5181,6 +5146,21 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5195,51 +5175,56 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446053</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136097900</v>
+        <v>132446056</v>
       </c>
       <c r="B43" t="n">
-        <v>111644</v>
+        <v>8460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348618</v>
+        <v>348430</v>
       </c>
       <c r="R43" t="n">
-        <v>6519260</v>
+        <v>6519483</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5266,12 +5251,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5282,6 +5267,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5297,33 +5297,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/132446056</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136707423</v>
+        <v>132446053</v>
       </c>
       <c r="B44" t="n">
-        <v>106421</v>
+        <v>111471</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5334,14 +5334,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348660</v>
+        <v>348463</v>
       </c>
       <c r="R44" t="n">
-        <v>6519138</v>
+        <v>6519366</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5368,12 +5368,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5399,64 +5399,54 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707423</t>
+          <t>https://artportalen.se/Sighting/132446053</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121791871</v>
+        <v>136097900</v>
       </c>
       <c r="B45" t="n">
-        <v>101326</v>
+        <v>111644</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348561</v>
+        <v>348618</v>
       </c>
       <c r="R45" t="n">
-        <v>6519216</v>
+        <v>6519260</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5480,12 +5470,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5496,84 +5486,69 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791871</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121792063</v>
+        <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>101326</v>
+        <v>111670</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348553</v>
+        <v>348464</v>
       </c>
       <c r="R46" t="n">
-        <v>6519199</v>
+        <v>6519341</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5597,12 +5572,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5613,36 +5588,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792063</t>
+          <t>https://artportalen.se/Sighting/137153573</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121792253</v>
+        <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>101326</v>
+        <v>106425</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5650,47 +5620,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348514</v>
+        <v>348660</v>
       </c>
       <c r="R47" t="n">
-        <v>6519160</v>
+        <v>6519138</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5714,12 +5674,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5730,33 +5690,28 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792253</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121792318</v>
+        <v>121791871</v>
       </c>
       <c r="B48" t="n">
         <v>101326</v>
@@ -5801,10 +5756,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348459</v>
+        <v>348561</v>
       </c>
       <c r="R48" t="n">
-        <v>6519139</v>
+        <v>6519216</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5850,7 +5805,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5867,13 +5822,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792318</t>
+          <t>https://artportalen.se/Sighting/121791871</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121792399</v>
+        <v>121792063</v>
       </c>
       <c r="B49" t="n">
         <v>101326</v>
@@ -5918,10 +5873,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>348481</v>
+        <v>348553</v>
       </c>
       <c r="R49" t="n">
-        <v>6519252</v>
+        <v>6519199</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5984,13 +5939,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792399</t>
+          <t>https://artportalen.se/Sighting/121792063</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121792568</v>
+        <v>121792253</v>
       </c>
       <c r="B50" t="n">
         <v>101326</v>
@@ -6031,14 +5986,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>348486</v>
+        <v>348514</v>
       </c>
       <c r="R50" t="n">
-        <v>6519336</v>
+        <v>6519160</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6101,13 +6056,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792568</t>
+          <t>https://artportalen.se/Sighting/121792253</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121792607</v>
+        <v>121792318</v>
       </c>
       <c r="B51" t="n">
         <v>101326</v>
@@ -6148,14 +6103,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348455</v>
+        <v>348459</v>
       </c>
       <c r="R51" t="n">
-        <v>6519346</v>
+        <v>6519139</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6218,16 +6173,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792607</t>
+          <t>https://artportalen.se/Sighting/121792318</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132335808</v>
+        <v>121792399</v>
       </c>
       <c r="B52" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,16 +6208,26 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>348481</v>
       </c>
       <c r="R52" t="n">
-        <v>6519286</v>
+        <v>6519252</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6289,12 +6254,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6305,31 +6270,36 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335808</t>
+          <t>https://artportalen.se/Sighting/121792399</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132336006</v>
+        <v>121792568</v>
       </c>
       <c r="B53" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6355,16 +6325,26 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>348550</v>
+        <v>348486</v>
       </c>
       <c r="R53" t="n">
-        <v>6519223</v>
+        <v>6519336</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6391,12 +6371,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6408,35 +6388,35 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336006</t>
+          <t>https://artportalen.se/Sighting/121792568</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132336196</v>
+        <v>121792607</v>
       </c>
       <c r="B54" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6462,16 +6442,26 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>348529</v>
+        <v>348455</v>
       </c>
       <c r="R54" t="n">
-        <v>6519171</v>
+        <v>6519346</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6498,12 +6488,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6515,32 +6505,32 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336196</t>
+          <t>https://artportalen.se/Sighting/121792607</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132336478</v>
+        <v>132335808</v>
       </c>
       <c r="B55" t="n">
         <v>101403</v>
@@ -6571,14 +6561,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>348493</v>
+        <v>348481</v>
       </c>
       <c r="R55" t="n">
-        <v>6519126</v>
+        <v>6519286</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6636,13 +6626,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336478</t>
+          <t>https://artportalen.se/Sighting/132335808</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132446046</v>
+        <v>132336006</v>
       </c>
       <c r="B56" t="n">
         <v>101403</v>
@@ -6673,17 +6663,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>348506</v>
+        <v>348550</v>
       </c>
       <c r="R56" t="n">
-        <v>6519266</v>
+        <v>6519223</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6707,12 +6697,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6723,28 +6713,33 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446046</t>
+          <t>https://artportalen.se/Sighting/132336006</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132446050</v>
+        <v>132336196</v>
       </c>
       <c r="B57" t="n">
         <v>101403</v>
@@ -6775,17 +6770,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>348486</v>
+        <v>348529</v>
       </c>
       <c r="R57" t="n">
-        <v>6519319</v>
+        <v>6519171</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6809,12 +6804,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6825,28 +6820,33 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446050</t>
+          <t>https://artportalen.se/Sighting/132336196</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132446052</v>
+        <v>132336478</v>
       </c>
       <c r="B58" t="n">
         <v>101403</v>
@@ -6877,17 +6877,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>348480</v>
+        <v>348493</v>
       </c>
       <c r="R58" t="n">
-        <v>6519355</v>
+        <v>6519126</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6931,27 +6931,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446052</t>
+          <t>https://artportalen.se/Sighting/132336478</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132336005</v>
+        <v>132446046</v>
       </c>
       <c r="B59" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,37 +6959,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>348550</v>
+        <v>348506</v>
       </c>
       <c r="R59" t="n">
-        <v>6519223</v>
+        <v>6519266</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7013,12 +7013,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7029,36 +7029,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336005</t>
+          <t>https://artportalen.se/Sighting/132446046</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132446061</v>
+        <v>132446050</v>
       </c>
       <c r="B60" t="n">
-        <v>80403</v>
+        <v>101403</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,34 +7061,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003719</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>348457</v>
+        <v>348486</v>
       </c>
       <c r="R60" t="n">
-        <v>6519520</v>
+        <v>6519319</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7150,6 +7145,419 @@
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137153572</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Väst om Ranneberget, Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>348456</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6519159</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153572</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132336005</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336005</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132446061</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>348457</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6519520</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446061</t>
         </is>
@@ -7216,6 +7624,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2242,7 +2242,7 @@
         <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89301</v>
+        <v>89303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96688</v>
+        <v>96690</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>136707421</v>
       </c>
       <c r="B36" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89303</v>
+        <v>89316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96690</v>
+        <v>96703</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>136707421</v>
       </c>
       <c r="B36" t="n">
-        <v>91611</v>
+        <v>91624</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96703</v>
+        <v>96705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>136707421</v>
       </c>
       <c r="B36" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -4600,11 +4600,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89318</v>
+        <v>89321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96705</v>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>136707421</v>
       </c>
       <c r="B36" t="n">
-        <v>91626</v>
+        <v>91629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89321</v>
+        <v>89331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>136707418</v>
       </c>
       <c r="B16" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>136707421</v>
       </c>
       <c r="B36" t="n">
-        <v>91629</v>
+        <v>91639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>132446065</v>
       </c>
       <c r="B38" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>136707423</v>
       </c>
       <c r="B47" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89332</v>
+        <v>89335</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89335</v>
+        <v>89340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89340</v>
+        <v>89351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89351</v>
+        <v>89352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>137153571</v>
       </c>
       <c r="B8" t="n">
-        <v>89355</v>
+        <v>89359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137153576</v>
       </c>
       <c r="B35" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153573</v>
       </c>
       <c r="B46" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>137153572</v>
       </c>
       <c r="B62" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
